--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="98">
   <si>
     <t/>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>PDJJRN PRMEN JAHE100</t>
+  </si>
+  <si>
+    <t>20137575</t>
+  </si>
+  <si>
+    <t>POTATOQ BBQ 50G</t>
+  </si>
+  <si>
+    <t>20137576</t>
+  </si>
+  <si>
+    <t>POTATOQ RMPT LAUT 50</t>
   </si>
 </sst>
 </file>
@@ -685,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1475,6 +1487,46 @@
         <v>12</v>
       </c>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t/>
   </si>
@@ -136,12 +136,6 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20091411</t>
-  </si>
-  <si>
-    <t>NIASA SALE MST KJ150</t>
-  </si>
-  <si>
     <t>20124676</t>
   </si>
   <si>
@@ -218,12 +212,6 @@
   </si>
   <si>
     <t>TUNGGAL B MARIE250GR</t>
-  </si>
-  <si>
-    <t>20049706</t>
-  </si>
-  <si>
-    <t>PICNIC DODOL GRT 250</t>
   </si>
   <si>
     <t>20025507</t>
@@ -697,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1001,10 +989,10 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,10 +1009,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,13 +1026,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>16</v>
@@ -1081,7 +1069,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>16</v>
@@ -1101,10 +1089,10 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,10 +1109,10 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1141,7 +1129,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
@@ -1158,13 +1146,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1181,10 +1169,10 @@
         <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1201,10 +1189,10 @@
         <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1221,10 +1209,10 @@
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,10 +1229,10 @@
         <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1261,18 +1249,18 @@
         <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1281,18 +1269,18 @@
         <v>19</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1301,7 +1289,7 @@
         <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
@@ -1309,19 +1297,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
@@ -1329,22 +1317,22 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,10 +1349,10 @@
         <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1381,7 +1369,7 @@
         <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>35</v>
@@ -1401,10 +1389,10 @@
         <v>23</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1421,10 +1409,10 @@
         <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1441,10 +1429,10 @@
         <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1461,7 +1449,7 @@
         <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
@@ -1481,49 +1469,9 @@
         <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -244,7 +244,7 @@
     <t>20106148</t>
   </si>
   <si>
-    <t>KR.TOAST SOES CHO 51</t>
+    <t>KR.TOAST SOES CHO 72</t>
   </si>
   <si>
     <t>20094497</t>
